--- a/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:16</t>
+    <t xml:space="preserve">2026-09-10 01:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:30</t>
+    <t xml:space="preserve">2026-09-12 22:42</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:42</t>
+    <t xml:space="preserve">2026-09-24 00:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -490,7 +490,7 @@
         <v>2020</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>144.85</v>
+        <v>154.19</v>
       </c>
     </row>
     <row r="3">
@@ -507,7 +507,7 @@
         <v>2020</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>84.39</v>
+        <v>90.71</v>
       </c>
     </row>
     <row r="4">
@@ -524,7 +524,7 @@
         <v>2020</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>82</v>
+        <v>87.23</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         <v>2020</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>76.09</v>
+        <v>81.15</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:10</t>
+    <t xml:space="preserve">2026-10-02 16:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2020_arica y parinacota.xlsx
@@ -54,7 +54,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 16:16</t>
+    <t xml:space="preserve">2026-10-05 16:32</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
